--- a/results/monthly_investor_report_2026-06-26.xlsx
+++ b/results/monthly_investor_report_2026-06-26.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1286261716247234</v>
+        <v>0.1286261716247233</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12862.61716247234</v>
+        <v>12862.61716247233</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1429.420290398965</v>
+        <v>1429.420290398962</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>361.1171904995398</v>
+        <v>361.1171904995397</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>306.9595859379225</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.002015606474425</v>
+        <v>2.002015606474419</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09876010286701303</v>
+        <v>0.09876010286701312</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9876.010286701303</v>
+        <v>9876.010286701312</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>569.770274207949</v>
+        <v>569.7702742079515</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>43.00577092194722</v>
+        <v>43.00577092194723</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>38.16395266206861</v>
+        <v>38.16395266206862</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9397943629868905</v>
+        <v>0.939794362986896</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09418198775809977</v>
+        <v>0.09418198775809983</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9418.198775809977</v>
+        <v>9418.198775809982</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0768720835510508</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>723.9965631944689</v>
+        <v>723.9965631944693</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>389.2892582037049</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>338.6494229435847</v>
+        <v>338.6494229435848</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.216129384176888</v>
+        <v>1.216129384176894</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09292983765935728</v>
+        <v>0.09292983765935721</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9292.983765935727</v>
+        <v>9292.983765935722</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.5464301606291</v>
+        <v>396.546430160627</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>144.3057422434339</v>
@@ -1103,7 +1103,7 @@
         <v>131.2317517386179</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.8238767911137752</v>
+        <v>0.8238767911137712</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>49999.99999999999</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1443,7 +1443,7 @@
         <v>0.1012146812708825</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.1296241549962105</v>
@@ -1452,7 +1452,7 @@
         <v>357.8947714130368</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>361.1171904995398</v>
+        <v>361.1171904995397</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>367.1278503737684</v>
@@ -1557,7 +1557,7 @@
         <v>-0.0037105180381591</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0219942686510214</v>
+        <v>0.0219942686510217</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>0.0938733706755232</v>
@@ -1611,25 +1611,25 @@
         <v>40.65999984741211</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0234457107155366</v>
+        <v>-0.0234457107155365</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.2257407445924774</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>39.70669725329592</v>
+        <v>39.70669725329593</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>43.00577092194722</v>
+        <v>43.00577092194723</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>49.83861848809694</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>38.16395266206861</v>
+        <v>38.16395266206862</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>-0.0557185041218549</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0.0731182729479942</v>
@@ -1680,7 +1680,7 @@
         <v>312.3211047616965</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>331.9915573116817</v>
+        <v>331.9915573116818</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>354.9338687775491</v>
@@ -1728,10 +1728,10 @@
         <v>-0.0082889988742848</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1593907013593682</v>
+        <v>0.159390701359368</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>137.2527965028754</v>
@@ -1857,7 +1857,7 @@
         <v>425.1313564101224</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>338.6494229435847</v>
+        <v>338.6494229435848</v>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
         <v>0.1926605504587155</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.4041814534285399</v>
+        <v>0.4041814534285401</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.0254876783377191</v>
@@ -2151,7 +2151,7 @@
         <v>0.0277544831724269</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
     </row>
     <row r="5">
@@ -2237,7 +2237,7 @@
         <v>0.0199787850023338</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0219942686510214</v>
+        <v>0.0219942686510217</v>
       </c>
     </row>
     <row r="7">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0306941366786843</v>
+        <v>0.0306941366786842</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
     </row>
     <row r="8">
@@ -2323,7 +2323,7 @@
         <v>0.0225893046698586</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
     </row>
     <row r="9">
@@ -2366,7 +2366,7 @@
         <v>0.0258968297470734</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
     </row>
     <row r="10">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0.0316052241444195</v>
+        <v>0.0316052241444194</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>0.0768720835510508</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.023328758071726</v>
+        <v>0.0233287580717261</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>-0.0144632354250776</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.0481226364410856</v>
+        <v>0.0481226364410858</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>0.0470152865980195</v>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.0592390972635019</v>
+        <v>0.0592390972635021</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.1007848660939432</v>
+        <v>0.1007848660939434</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.1703970939841539</v>
+        <v>0.1703970939841541</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>-0.09047421021702989</v>
@@ -2581,7 +2581,7 @@
         <v>0.0257353684650022</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.06255951557298681</v>
+        <v>0.0625595155729869</v>
       </c>
     </row>
     <row r="15">
@@ -2607,7 +2607,7 @@
         <v>0.0249554181347848</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.1601752428145885</v>
+        <v>-0.1601752428145886</v>
       </c>
       <c r="G15" s="24" t="n">
         <v>-0.0619335174456089</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.021857194251186</v>
+        <v>0.0218571942511859</v>
       </c>
       <c r="K16" s="24" t="n">
         <v>0.0477932433117227</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.0268138653389995</v>
+        <v>0.0268138653389994</v>
       </c>
       <c r="K17" s="24" t="n">
         <v>0.0236686907772818</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.0038572954450379</v>
+        <v>0.0038572954450377</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.064690066309239</v>
+        <v>-0.0646900663092389</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>-0.0378927780939064</v>
+        <v>-0.0378927780939065</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>-0.1473805790456531</v>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-0.1140271680663239</v>
+        <v>-0.114027168066324</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.0213875767230238</v>
+        <v>0.0213875767230236</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>0.1773903133981555</v>
+        <v>0.1773903133981553</v>
       </c>
       <c r="H19" s="24" t="n">
         <v>-0.2178459598945363</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.0223518238238337</v>
+        <v>0.0223518238238338</v>
       </c>
       <c r="K20" s="24" t="n">
         <v>0.0999999916062814</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3675,13 +3675,13 @@
         <v>101.5</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>97.44999694824219</v>
+        <v>97.4499969482422</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.03990150789909175</v>
+        <v>-0.03990150789909164</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>-28378.26246333471</v>
+        <v>-28378.2624633346</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>2256106.809120123</v>

--- a/results/monthly_investor_report_2026-06-26.xlsx
+++ b/results/monthly_investor_report_2026-06-26.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14259.7998046875</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12525.76452636719</v>
+        <v>12543.48702636719</v>
       </c>
     </row>
     <row r="6">
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3447,7 +3447,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="5">
@@ -3477,7 +3477,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="6">
@@ -3507,7 +3507,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="7">
@@ -3537,7 +3537,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="8">
@@ -3567,7 +3567,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="9">
@@ -3597,7 +3597,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="10">
@@ -3627,7 +3627,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="11">
@@ -3657,7 +3657,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="12">
@@ -3687,7 +3687,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="13">
@@ -3717,7 +3717,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="14">
@@ -3747,7 +3747,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
   </sheetData>
